--- a/grupos/1BM - Estadisticos 20221.xlsx
+++ b/grupos/1BM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="140">
   <si>
     <t>Materia</t>
   </si>
@@ -86,9 +86,6 @@
     <t>GOMEZ GONZALEZ FEDERICO ABIMAEL</t>
   </si>
   <si>
-    <t>GUTIERREZ OLVERA HORACIO</t>
-  </si>
-  <si>
     <t>HERNANDEZ MENDOZA DAMIAN</t>
   </si>
   <si>
@@ -185,15 +182,15 @@
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
+    <t>Herrera Serrano Mayra Iliana</t>
+  </si>
+  <si>
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
-    <t>Herrera Serrano Mayra Iliana</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -212,208 +209,202 @@
     <t>GALVEZ</t>
   </si>
   <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>JENKINS</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>PALOMINO</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>AMAYO</t>
+  </si>
+  <si>
+    <t>ACOSTA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>SALOMON</t>
+  </si>
+  <si>
+    <t>CARLOS YAEL</t>
+  </si>
+  <si>
+    <t>DYLAN</t>
+  </si>
+  <si>
+    <t>MIGUEL ANTONIO</t>
+  </si>
+  <si>
+    <t>ARTHUR RICHARD</t>
+  </si>
+  <si>
+    <t>ERIC</t>
+  </si>
+  <si>
+    <t>AARON MIGUEL</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>ALVARADO</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CRESCENCIO</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
     <t>GIL</t>
   </si>
   <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>PALESTINO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>TOLEDO</t>
+  </si>
+  <si>
+    <t>XOCHICALE</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>LOMAS</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>JENKINS</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>PALOMINO</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>AMAYO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>OLVERA</t>
-  </si>
-  <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>SALOMON</t>
-  </si>
-  <si>
-    <t>CARLOS YAEL</t>
-  </si>
-  <si>
-    <t>DYLAN</t>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>TEQUILIQUIHUA</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>AXEL MICHAELL</t>
+  </si>
+  <si>
+    <t>ALVARO OZIEL</t>
+  </si>
+  <si>
+    <t>RICARDO</t>
+  </si>
+  <si>
+    <t>SIMON</t>
+  </si>
+  <si>
+    <t>DIEGO ARMANDO</t>
+  </si>
+  <si>
+    <t>JUAN PABLO</t>
   </si>
   <si>
     <t>JOSE RAUL</t>
   </si>
   <si>
-    <t>HORACIO</t>
-  </si>
-  <si>
-    <t>MIGUEL ANTONIO</t>
-  </si>
-  <si>
-    <t>ARTHUR RICHARD</t>
-  </si>
-  <si>
-    <t>ERIC</t>
+    <t>FEDERICO ABIMAEL</t>
+  </si>
+  <si>
+    <t>DAMIAN</t>
+  </si>
+  <si>
+    <t>ROGGER JUSEFH</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
   </si>
   <si>
     <t>KARLA ABIGAIL</t>
-  </si>
-  <si>
-    <t>AARON MIGUEL</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>ALVARADO</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CRESCENCIO</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PALESTINO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>TOLEDO</t>
-  </si>
-  <si>
-    <t>XOCHICALE</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>LOMAS</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>TEQUILIQUIHUA</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>AXEL MICHAELL</t>
-  </si>
-  <si>
-    <t>ALVARO OZIEL</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>SIMON</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t>JUAN PABLO</t>
-  </si>
-  <si>
-    <t>FEDERICO ABIMAEL</t>
-  </si>
-  <si>
-    <t>DAMIAN</t>
-  </si>
-  <si>
-    <t>ROGGER JUSEFH</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
   </si>
   <si>
     <t>GUILLERMO JESUS</t>
@@ -804,7 +795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y34"/>
+  <dimension ref="A1:Y33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -950,19 +941,19 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -986,13 +977,13 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U4">
         <v>9</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W4">
         <v>8</v>
@@ -1027,19 +1018,19 @@
         <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1063,7 +1054,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U5">
         <v>9</v>
@@ -1104,19 +1095,19 @@
         <v>7</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I6">
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -1140,13 +1131,13 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U6">
         <v>10</v>
       </c>
       <c r="V6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>6</v>
@@ -1181,19 +1172,19 @@
         <v>9</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K7">
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1217,7 +1208,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U7">
         <v>9</v>
@@ -1229,7 +1220,7 @@
         <v>8</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>9</v>
@@ -1258,19 +1249,19 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1306,7 +1297,7 @@
         <v>8</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -1335,19 +1326,19 @@
         <v>6</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I9">
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1377,7 +1368,7 @@
         <v>8</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>8</v>
@@ -1418,13 +1409,13 @@
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K10">
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1454,7 +1445,7 @@
         <v>10</v>
       </c>
       <c r="V10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W10">
         <v>7</v>
@@ -1495,13 +1486,13 @@
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K11">
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1531,13 +1522,13 @@
         <v>7</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W11">
         <v>8</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y11">
         <v>6</v>
@@ -1554,7 +1545,7 @@
         <v>5</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E12">
         <v>7</v>
@@ -1566,19 +1557,19 @@
         <v>8</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I12">
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1608,7 +1599,7 @@
         <v>5</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>7</v>
@@ -1643,19 +1634,19 @@
         <v>8</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I13">
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1702,37 +1693,37 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I14">
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1756,22 +1747,22 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1779,13 +1770,13 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="C15">
         <v>8</v>
       </c>
       <c r="D15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E15">
         <v>7</v>
@@ -1803,13 +1794,13 @@
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1833,13 +1824,13 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="U15">
         <v>8</v>
       </c>
       <c r="V15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>7</v>
@@ -1859,19 +1850,19 @@
         <v>-1</v>
       </c>
       <c r="C16">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D16">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E16">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H16">
         <v>-1</v>
@@ -1880,13 +1871,13 @@
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -1913,19 +1904,19 @@
         <v>-1</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X16">
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1933,37 +1924,37 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17">
         <v>5</v>
       </c>
       <c r="E17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I17">
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -1987,22 +1978,22 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V17">
         <v>5</v>
       </c>
       <c r="W17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2010,22 +2001,22 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="C18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18">
         <v>5</v>
       </c>
       <c r="E18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F18">
         <v>6</v>
       </c>
       <c r="G18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H18">
         <v>-1</v>
@@ -2040,7 +2031,7 @@
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -2064,22 +2055,22 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="U18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V18">
         <v>5</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2087,37 +2078,37 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C19">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I19">
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -2141,22 +2132,22 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2167,34 +2158,34 @@
         <v>8</v>
       </c>
       <c r="C20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G20">
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I20">
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -2218,16 +2209,16 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V20">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X20">
         <v>7</v>
@@ -2244,34 +2235,34 @@
         <v>8</v>
       </c>
       <c r="C21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D21">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G21">
         <v>6</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I21">
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2295,19 +2286,19 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>6</v>
@@ -2318,22 +2309,22 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="C22">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D22">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H22">
         <v>-1</v>
@@ -2342,13 +2333,13 @@
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2372,22 +2363,22 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V22">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="W22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2395,37 +2386,37 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D23">
         <v>5</v>
       </c>
       <c r="E23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G23">
         <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I23">
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
         <v>-1</v>
@@ -2449,19 +2440,19 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>5</v>
       </c>
       <c r="W23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -2475,34 +2466,34 @@
         <v>6</v>
       </c>
       <c r="C24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F24">
         <v>6</v>
       </c>
       <c r="G24">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I24">
         <v>-1</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2526,22 +2517,22 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V24">
         <v>5</v>
       </c>
       <c r="W24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y24">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2555,31 +2546,31 @@
         <v>5</v>
       </c>
       <c r="D25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F25">
         <v>6</v>
       </c>
       <c r="G25">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I25">
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K25">
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2603,22 +2594,22 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U25">
         <v>5</v>
       </c>
       <c r="V25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2626,16 +2617,16 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C26">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D26">
         <v>5</v>
       </c>
       <c r="E26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F26">
         <v>6</v>
@@ -2644,19 +2635,19 @@
         <v>6</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I26">
         <v>-1</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K26">
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2680,19 +2671,19 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U26">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V26">
         <v>5</v>
       </c>
       <c r="W26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y26">
         <v>6</v>
@@ -2703,16 +2694,16 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C27">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E27">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F27">
         <v>6</v>
@@ -2721,7 +2712,7 @@
         <v>6</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -2733,7 +2724,7 @@
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M27">
         <v>-1</v>
@@ -2757,19 +2748,19 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U27">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y27">
         <v>6</v>
@@ -2783,10 +2774,10 @@
         <v>6</v>
       </c>
       <c r="C28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E28">
         <v>6</v>
@@ -2798,19 +2789,19 @@
         <v>6</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I28">
         <v>-1</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -2834,13 +2825,13 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W28">
         <v>6</v>
@@ -2857,37 +2848,37 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D29">
         <v>8</v>
       </c>
       <c r="E29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I29">
         <v>-1</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K29">
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -2911,22 +2902,22 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V29">
         <v>8</v>
       </c>
       <c r="W29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2934,19 +2925,19 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="C30">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E30">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G30">
         <v>7</v>
@@ -2958,13 +2949,13 @@
         <v>-1</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K30">
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -2988,19 +2979,19 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="U30">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y30">
         <v>7</v>
@@ -3011,37 +3002,37 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C31">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I31">
         <v>-1</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K31">
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -3065,22 +3056,22 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U31">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y31">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3088,37 +3079,37 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D32">
         <v>8</v>
       </c>
       <c r="E32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F32">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G32">
         <v>6</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I32">
         <v>-1</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K32">
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -3145,16 +3136,16 @@
         <v>8</v>
       </c>
       <c r="U32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V32">
         <v>8</v>
       </c>
       <c r="W32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y32">
         <v>6</v>
@@ -3177,25 +3168,25 @@
         <v>8</v>
       </c>
       <c r="F33">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I33">
         <v>-1</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K33">
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -3231,86 +3222,9 @@
         <v>8</v>
       </c>
       <c r="X33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y33">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:25">
-      <c r="A34" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B34">
-        <v>9</v>
-      </c>
-      <c r="C34">
-        <v>10</v>
-      </c>
-      <c r="D34">
-        <v>8</v>
-      </c>
-      <c r="E34">
-        <v>8</v>
-      </c>
-      <c r="F34">
-        <v>9</v>
-      </c>
-      <c r="G34">
-        <v>8</v>
-      </c>
-      <c r="H34">
-        <v>-1</v>
-      </c>
-      <c r="I34">
-        <v>-1</v>
-      </c>
-      <c r="J34">
-        <v>-1</v>
-      </c>
-      <c r="K34">
-        <v>-1</v>
-      </c>
-      <c r="L34">
-        <v>-1</v>
-      </c>
-      <c r="M34">
-        <v>-1</v>
-      </c>
-      <c r="N34">
-        <v>-1</v>
-      </c>
-      <c r="O34">
-        <v>-1</v>
-      </c>
-      <c r="P34">
-        <v>-1</v>
-      </c>
-      <c r="Q34">
-        <v>-1</v>
-      </c>
-      <c r="R34">
-        <v>-1</v>
-      </c>
-      <c r="S34">
-        <v>-1</v>
-      </c>
-      <c r="T34">
-        <v>9</v>
-      </c>
-      <c r="U34">
-        <v>10</v>
-      </c>
-      <c r="V34">
-        <v>8</v>
-      </c>
-      <c r="W34">
-        <v>8</v>
-      </c>
-      <c r="X34">
-        <v>9</v>
-      </c>
-      <c r="Y34">
         <v>8</v>
       </c>
     </row>
@@ -3338,31 +3252,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -3370,31 +3284,31 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>67.73999999999999</v>
+        <v>60</v>
       </c>
       <c r="G2">
-        <v>25.81</v>
+        <v>40</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3402,31 +3316,31 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>74.19</v>
+        <v>63.33</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>13.33</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J3">
-        <v>25.81</v>
+        <v>23.33</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3434,10 +3348,10 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C4">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4">
         <v>23</v>
@@ -3446,45 +3360,45 @@
         <v>7</v>
       </c>
       <c r="F4">
-        <v>74.19</v>
+        <v>76.67</v>
       </c>
       <c r="G4">
-        <v>22.58</v>
+        <v>23.33</v>
       </c>
       <c r="H4">
         <v>7.8</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>3.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E5">
         <v>5</v>
       </c>
       <c r="F5">
-        <v>83.87</v>
+        <v>83.33</v>
       </c>
       <c r="G5">
-        <v>16.13</v>
+        <v>16.67</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3495,28 +3409,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C6">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D6">
         <v>26</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>83.87</v>
+        <v>86.67</v>
       </c>
       <c r="G6">
-        <v>16.13</v>
+        <v>13.33</v>
       </c>
       <c r="H6">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3527,34 +3441,34 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C7">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D7">
         <v>26</v>
       </c>
       <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <v>86.67</v>
+      </c>
+      <c r="G7">
+        <v>13.33</v>
+      </c>
+      <c r="H7">
+        <v>6.6</v>
+      </c>
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>83.87</v>
-      </c>
-      <c r="G7">
+      <c r="J7">
         <v>0</v>
-      </c>
-      <c r="H7">
-        <v>6.8</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>16.13</v>
       </c>
     </row>
   </sheetData>
@@ -3564,7 +3478,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3573,16 +3487,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -3596,19 +3510,19 @@
         <v>22330051920034</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3616,36 +3530,36 @@
         <v>22330051920035</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920036</v>
+        <v>22330051920038</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>52</v>
@@ -3653,19 +3567,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920324</v>
+        <v>22330051920189</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
         <v>52</v>
@@ -3673,242 +3587,62 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920324</v>
+        <v>22330051920325</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920324</v>
+        <v>22330051920043</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920324</v>
+        <v>22330051920049</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>22330051920038</v>
-      </c>
-      <c r="B9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>22330051920189</v>
-      </c>
-      <c r="B10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>22330051920189</v>
-      </c>
-      <c r="B11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D11" t="s">
-        <v>87</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>22330051920325</v>
-      </c>
-      <c r="B12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" t="s">
-        <v>78</v>
-      </c>
-      <c r="D12" t="s">
-        <v>88</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>22330051920041</v>
-      </c>
-      <c r="B13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" t="s">
-        <v>79</v>
-      </c>
-      <c r="D13" t="s">
-        <v>89</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>22330051920043</v>
-      </c>
-      <c r="B14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" t="s">
-        <v>80</v>
-      </c>
-      <c r="D14" t="s">
-        <v>90</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>22330051920043</v>
-      </c>
-      <c r="B15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" t="s">
-        <v>80</v>
-      </c>
-      <c r="D15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>22330051920049</v>
-      </c>
-      <c r="B16" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" t="s">
-        <v>81</v>
-      </c>
-      <c r="D16" t="s">
-        <v>91</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>22330051920049</v>
-      </c>
-      <c r="B17" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" t="s">
-        <v>81</v>
-      </c>
-      <c r="D17" t="s">
-        <v>91</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -3918,7 +3652,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3927,101 +3661,101 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>22330051920324</v>
+        <v>22330051920034</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
         <v>75</v>
       </c>
-      <c r="D2" t="s">
-        <v>85</v>
-      </c>
       <c r="E2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>22330051920189</v>
+        <v>22330051920035</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>22330051920043</v>
+        <v>22330051920038</v>
       </c>
       <c r="B4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" t="s">
         <v>70</v>
       </c>
-      <c r="C4" t="s">
-        <v>80</v>
-      </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>22330051920049</v>
+        <v>22330051920189</v>
       </c>
       <c r="B5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" t="s">
         <v>71</v>
       </c>
-      <c r="C5" t="s">
-        <v>81</v>
-      </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>22330051920034</v>
+        <v>22330051920325</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
         <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -4029,16 +3763,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>22330051920035</v>
+        <v>22330051920043</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
         <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -4046,16 +3780,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>22330051920036</v>
+        <v>22330051920049</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
         <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -4063,67 +3797,67 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>22330051920038</v>
+        <v>22330051920029</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>22330051920325</v>
+        <v>22330051920030</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>22330051920041</v>
+        <v>22330051920031</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>22330051920029</v>
+        <v>22330051920032</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -4131,16 +3865,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>22330051920030</v>
+        <v>22330051920033</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="D13" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -4148,16 +3882,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>22330051920031</v>
+        <v>22330051920323</v>
       </c>
       <c r="B14" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>110</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -4165,16 +3899,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>22330051920032</v>
+        <v>22330051920036</v>
       </c>
       <c r="B15" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -4182,16 +3916,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>22330051920033</v>
+        <v>22330051920037</v>
       </c>
       <c r="B16" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C16" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="D16" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -4199,16 +3933,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>22330051920323</v>
+        <v>22330051920331</v>
       </c>
       <c r="B17" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D17" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -4216,16 +3950,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>22330051920037</v>
+        <v>22330051920039</v>
       </c>
       <c r="B18" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C18" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -4233,16 +3967,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>22330051920331</v>
+        <v>22330051920040</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4250,16 +3984,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>22330051920039</v>
+        <v>22330051920041</v>
       </c>
       <c r="B20" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C20" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D20" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -4267,16 +4001,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>22330051920040</v>
+        <v>22330051920042</v>
       </c>
       <c r="B21" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -4284,16 +4018,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>22330051920042</v>
+        <v>22330051920327</v>
       </c>
       <c r="B22" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C22" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D22" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -4301,16 +4035,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>22330051920327</v>
+        <v>22330051920044</v>
       </c>
       <c r="B23" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D23" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -4318,16 +4052,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>22330051920044</v>
+        <v>22330051920045</v>
       </c>
       <c r="B24" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D24" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -4335,16 +4069,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>22330051920045</v>
+        <v>22330051920046</v>
       </c>
       <c r="B25" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="C25" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D25" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -4352,16 +4086,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>22330051920046</v>
+        <v>22330051920328</v>
       </c>
       <c r="B26" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="C26" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D26" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -4369,16 +4103,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>22330051920328</v>
+        <v>22330051920047</v>
       </c>
       <c r="B27" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C27" t="s">
-        <v>65</v>
+        <v>111</v>
       </c>
       <c r="D27" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -4386,16 +4120,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>22330051920047</v>
+        <v>22330051920048</v>
       </c>
       <c r="B28" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C28" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -4403,16 +4137,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>22330051920048</v>
+        <v>22330051920329</v>
       </c>
       <c r="B29" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C29" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D29" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -4420,16 +4154,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>22330051920329</v>
+        <v>22330051920050</v>
       </c>
       <c r="B30" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C30" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D30" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -4437,35 +4171,18 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>22330051920050</v>
+        <v>22330051920051</v>
       </c>
       <c r="B31" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D31" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32">
-        <v>22330051920051</v>
-      </c>
-      <c r="B32" t="s">
-        <v>108</v>
-      </c>
-      <c r="C32" t="s">
-        <v>121</v>
-      </c>
-      <c r="D32" t="s">
-        <v>142</v>
-      </c>
-      <c r="E32">
         <v>0</v>
       </c>
     </row>
@@ -4476,7 +4193,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4485,22 +4202,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -4508,111 +4225,111 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920036</v>
+        <v>22330051920034</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920036</v>
+        <v>22330051920034</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920041</v>
+        <v>22330051920035</v>
       </c>
       <c r="B4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" t="s">
         <v>69</v>
       </c>
-      <c r="C4" t="s">
-        <v>79</v>
-      </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>52</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920041</v>
+        <v>22330051920035</v>
       </c>
       <c r="B5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" t="s">
         <v>69</v>
       </c>
-      <c r="C5" t="s">
-        <v>79</v>
-      </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920044</v>
+        <v>22330051920047</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
         <v>52</v>
@@ -4623,22 +4340,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920044</v>
+        <v>22330051920047</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4646,22 +4363,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920045</v>
+        <v>22330051920036</v>
       </c>
       <c r="B8" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="D8" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4669,162 +4386,93 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920045</v>
+        <v>22330051920038</v>
       </c>
       <c r="B9" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="D9" t="s">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
         <v>52</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920034</v>
+        <v>22330051920039</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920035</v>
+        <v>22330051920041</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="D11" t="s">
-        <v>83</v>
+        <v>128</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920038</v>
+        <v>22330051920046</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="D12" t="s">
-        <v>86</v>
+        <v>133</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920039</v>
-      </c>
-      <c r="B13" t="s">
-        <v>99</v>
-      </c>
-      <c r="C13" t="s">
-        <v>111</v>
-      </c>
-      <c r="D13" t="s">
-        <v>130</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>52</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920327</v>
-      </c>
-      <c r="B14" t="s">
-        <v>102</v>
-      </c>
-      <c r="C14" t="s">
-        <v>114</v>
-      </c>
-      <c r="D14" t="s">
-        <v>133</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920046</v>
-      </c>
-      <c r="B15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" t="s">
-        <v>117</v>
-      </c>
-      <c r="D15" t="s">
-        <v>136</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>52</v>
-      </c>
-      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1BM - Estadisticos 20221.xlsx
+++ b/grupos/1BM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="140">
   <si>
     <t>Materia</t>
   </si>
@@ -179,13 +179,13 @@
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
+    <t>Herrera Serrano Mayra Iliana</t>
+  </si>
+  <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
     <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
-    <t>Herrera Serrano Mayra Iliana</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
     <t>Velasco Sánchez David</t>
@@ -944,13 +944,13 @@
         <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
         <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
         <v>7</v>
@@ -980,13 +980,13 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V4">
         <v>9</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>7</v>
@@ -1021,13 +1021,13 @@
         <v>8</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J5">
         <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
         <v>8</v>
@@ -1057,7 +1057,7 @@
         <v>9</v>
       </c>
       <c r="U5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V5">
         <v>9</v>
@@ -1098,13 +1098,13 @@
         <v>6</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J6">
         <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
         <v>6</v>
@@ -1134,13 +1134,13 @@
         <v>7</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V6">
         <v>8</v>
       </c>
       <c r="W6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>6</v>
@@ -1175,13 +1175,13 @@
         <v>7</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
         <v>9</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L7">
         <v>9</v>
@@ -1211,7 +1211,7 @@
         <v>9</v>
       </c>
       <c r="U7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V7">
         <v>9</v>
@@ -1252,13 +1252,13 @@
         <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
         <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>9</v>
@@ -1294,7 +1294,7 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -1329,13 +1329,13 @@
         <v>9</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
         <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
         <v>7</v>
@@ -1365,7 +1365,7 @@
         <v>10</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V9">
         <v>9</v>
@@ -1406,13 +1406,13 @@
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J10">
         <v>5</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
         <v>6</v>
@@ -1442,13 +1442,13 @@
         <v>-1</v>
       </c>
       <c r="U10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V10">
         <v>5</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>6</v>
@@ -1489,7 +1489,7 @@
         <v>5</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
         <v>7</v>
@@ -1525,7 +1525,7 @@
         <v>5</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>7</v>
@@ -1560,13 +1560,13 @@
         <v>8</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J12">
         <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
         <v>6</v>
@@ -1596,13 +1596,13 @@
         <v>9</v>
       </c>
       <c r="U12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V12">
         <v>8</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>6</v>
@@ -1637,13 +1637,13 @@
         <v>9</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J13">
         <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
         <v>8</v>
@@ -1679,7 +1679,7 @@
         <v>8</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -1714,13 +1714,13 @@
         <v>8</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J14">
         <v>7</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
         <v>7</v>
@@ -1750,7 +1750,7 @@
         <v>7</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V14">
         <v>8</v>
@@ -1791,13 +1791,13 @@
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J15">
         <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
         <v>6</v>
@@ -1827,7 +1827,7 @@
         <v>-1</v>
       </c>
       <c r="U15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V15">
         <v>8</v>
@@ -1868,13 +1868,13 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
         <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
         <v>7</v>
@@ -1945,13 +1945,13 @@
         <v>6</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
         <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
         <v>6</v>
@@ -2022,13 +2022,13 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L18">
         <v>5</v>
@@ -2099,13 +2099,13 @@
         <v>6</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J19">
         <v>5</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
         <v>8</v>
@@ -2141,7 +2141,7 @@
         <v>7</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X19">
         <v>8</v>
@@ -2182,7 +2182,7 @@
         <v>6</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
         <v>7</v>
@@ -2253,13 +2253,13 @@
         <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
         <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
         <v>6</v>
@@ -2295,7 +2295,7 @@
         <v>9</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2330,13 +2330,13 @@
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J22">
         <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
         <v>6</v>
@@ -2407,13 +2407,13 @@
         <v>5</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
         <v>5</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
         <v>6</v>
@@ -2484,13 +2484,13 @@
         <v>5</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J24">
         <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
         <v>7</v>
@@ -2520,13 +2520,13 @@
         <v>5</v>
       </c>
       <c r="U24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V24">
         <v>5</v>
       </c>
       <c r="W24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X24">
         <v>7</v>
@@ -2561,13 +2561,13 @@
         <v>5</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J25">
         <v>5</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L25">
         <v>5</v>
@@ -2597,13 +2597,13 @@
         <v>5</v>
       </c>
       <c r="U25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V25">
         <v>5</v>
       </c>
       <c r="W25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X25">
         <v>5</v>
@@ -2638,13 +2638,13 @@
         <v>6</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J26">
         <v>6</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
         <v>7</v>
@@ -2674,7 +2674,7 @@
         <v>8</v>
       </c>
       <c r="U26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V26">
         <v>5</v>
@@ -2715,13 +2715,13 @@
         <v>5</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
         <v>5</v>
@@ -2754,10 +2754,10 @@
         <v>7</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X27">
         <v>5</v>
@@ -2792,13 +2792,13 @@
         <v>8</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J28">
         <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
         <v>6</v>
@@ -2828,13 +2828,13 @@
         <v>7</v>
       </c>
       <c r="U28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V28">
         <v>8</v>
       </c>
       <c r="W28">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>6</v>
@@ -2869,13 +2869,13 @@
         <v>7</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J29">
         <v>7</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
         <v>8</v>
@@ -2911,7 +2911,7 @@
         <v>8</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X29">
         <v>8</v>
@@ -2946,13 +2946,13 @@
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J30">
         <v>5</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L30">
         <v>6</v>
@@ -3023,13 +3023,13 @@
         <v>8</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J31">
         <v>7</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L31">
         <v>7</v>
@@ -3059,13 +3059,13 @@
         <v>8</v>
       </c>
       <c r="U31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V31">
         <v>8</v>
       </c>
       <c r="W31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X31">
         <v>8</v>
@@ -3100,13 +3100,13 @@
         <v>6</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J32">
         <v>7</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
         <v>7</v>
@@ -3136,13 +3136,13 @@
         <v>8</v>
       </c>
       <c r="U32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V32">
         <v>8</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X32">
         <v>7</v>
@@ -3177,13 +3177,13 @@
         <v>9</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J33">
         <v>8</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L33">
         <v>7</v>
@@ -3213,13 +3213,13 @@
         <v>9</v>
       </c>
       <c r="U33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V33">
         <v>8</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X33">
         <v>8</v>
@@ -3345,7 +3345,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>53</v>
@@ -3354,19 +3354,19 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>76.67</v>
+        <v>83.33</v>
       </c>
       <c r="G4">
-        <v>23.33</v>
+        <v>16.67</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3377,7 +3377,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
@@ -3386,19 +3386,19 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>83.33</v>
+        <v>86.67</v>
       </c>
       <c r="G5">
-        <v>16.67</v>
+        <v>13.33</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3409,7 +3409,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
@@ -3430,7 +3430,7 @@
         <v>13.33</v>
       </c>
       <c r="H6">
-        <v>6.9</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4193,7 +4193,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4317,16 +4317,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920047</v>
+        <v>22330051920327</v>
       </c>
       <c r="B6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D6" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -4340,22 +4340,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920047</v>
+        <v>22330051920327</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D7" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4363,22 +4363,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920036</v>
+        <v>22330051920047</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D8" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4386,62 +4386,62 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920038</v>
+        <v>22330051920047</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="D9" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920039</v>
+        <v>22330051920038</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
-        <v>126</v>
+        <v>77</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920041</v>
+        <v>22330051920039</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -4455,16 +4455,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920046</v>
+        <v>22330051920041</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D12" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -4473,6 +4473,29 @@
         <v>51</v>
       </c>
       <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920046</v>
+      </c>
+      <c r="B13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D13" t="s">
+        <v>133</v>
+      </c>
+      <c r="E13" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1BM - Estadisticos 20221.xlsx
+++ b/grupos/1BM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="140">
   <si>
     <t>Materia</t>
   </si>
@@ -179,6 +179,9 @@
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
@@ -186,9 +189,6 @@
   </si>
   <si>
     <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
-    <t>Velasco Sánchez David</t>
   </si>
   <si>
     <t>NC</t>
@@ -956,7 +956,7 @@
         <v>7</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1033,7 +1033,7 @@
         <v>8</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1110,7 +1110,7 @@
         <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1187,7 +1187,7 @@
         <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1264,7 +1264,7 @@
         <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1341,7 +1341,7 @@
         <v>7</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1418,7 +1418,7 @@
         <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1454,7 +1454,7 @@
         <v>6</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1495,7 +1495,7 @@
         <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1572,7 +1572,7 @@
         <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1649,7 +1649,7 @@
         <v>8</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1726,7 +1726,7 @@
         <v>7</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1803,7 +1803,7 @@
         <v>6</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1880,7 +1880,7 @@
         <v>7</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1957,7 +1957,7 @@
         <v>6</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1993,7 +1993,7 @@
         <v>6</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2034,7 +2034,7 @@
         <v>5</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2111,7 +2111,7 @@
         <v>8</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2147,7 +2147,7 @@
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2188,7 +2188,7 @@
         <v>7</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2224,7 +2224,7 @@
         <v>7</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2265,7 +2265,7 @@
         <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2301,7 +2301,7 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2342,7 +2342,7 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2419,7 +2419,7 @@
         <v>6</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2496,7 +2496,7 @@
         <v>7</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2573,7 +2573,7 @@
         <v>5</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2650,7 +2650,7 @@
         <v>7</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2727,7 +2727,7 @@
         <v>5</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2763,7 +2763,7 @@
         <v>5</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2804,7 +2804,7 @@
         <v>6</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2881,7 +2881,7 @@
         <v>8</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2958,7 +2958,7 @@
         <v>6</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2994,7 +2994,7 @@
         <v>5</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3035,7 +3035,7 @@
         <v>7</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3071,7 +3071,7 @@
         <v>8</v>
       </c>
       <c r="Y31">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3112,7 +3112,7 @@
         <v>7</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3189,7 +3189,7 @@
         <v>7</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3225,7 +3225,7 @@
         <v>8</v>
       </c>
       <c r="Y33">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3345,7 +3345,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>53</v>
@@ -3366,7 +3366,7 @@
         <v>16.67</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3377,7 +3377,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
@@ -3386,19 +3386,19 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>86.67</v>
+        <v>83.33</v>
       </c>
       <c r="G5">
-        <v>13.33</v>
+        <v>16.67</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3409,7 +3409,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
@@ -3430,7 +3430,7 @@
         <v>13.33</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3441,7 +3441,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>56</v>
@@ -3462,7 +3462,7 @@
         <v>13.33</v>
       </c>
       <c r="H7">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4193,7 +4193,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4363,16 +4363,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920047</v>
+        <v>22330051920038</v>
       </c>
       <c r="B8" t="s">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -4381,27 +4381,27 @@
         <v>52</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920047</v>
+        <v>22330051920039</v>
       </c>
       <c r="B9" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="D9" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4409,39 +4409,39 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920038</v>
+        <v>22330051920041</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="D10" t="s">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920039</v>
+        <v>22330051920046</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="D11" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -4450,52 +4450,6 @@
         <v>51</v>
       </c>
       <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920041</v>
-      </c>
-      <c r="B12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D12" t="s">
-        <v>128</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>51</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920046</v>
-      </c>
-      <c r="B13" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" t="s">
-        <v>111</v>
-      </c>
-      <c r="D13" t="s">
-        <v>133</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>51</v>
-      </c>
-      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1BM - Estadisticos 20221.xlsx
+++ b/grupos/1BM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="140">
   <si>
     <t>Materia</t>
   </si>
@@ -203,232 +203,232 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ALVARADO</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CRESCENCIO</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
     <t>GALVEZ</t>
   </si>
   <si>
+    <t>GIL</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
     <t>HERRERA</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>JENKINS</t>
   </si>
   <si>
+    <t>LUNA</t>
+  </si>
+  <si>
     <t>MENDOZA</t>
   </si>
   <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
     <t>PALOMINO</t>
   </si>
   <si>
+    <t>PALESTINO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>TOLEDO</t>
+  </si>
+  <si>
     <t>VENTURA</t>
   </si>
   <si>
-    <t>REYES</t>
+    <t>XOCHICALE</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
   </si>
   <si>
     <t>AMAYO</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>ACOSTA</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>LOMAS</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
   </si>
   <si>
     <t>SALOMON</t>
   </si>
   <si>
+    <t>TEQUILIQUIHUA</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>AXEL MICHAELL</t>
+  </si>
+  <si>
+    <t>ALVARO OZIEL</t>
+  </si>
+  <si>
+    <t>RICARDO</t>
+  </si>
+  <si>
+    <t>SIMON</t>
+  </si>
+  <si>
+    <t>DIEGO ARMANDO</t>
+  </si>
+  <si>
+    <t>JUAN PABLO</t>
+  </si>
+  <si>
     <t>CARLOS YAEL</t>
   </si>
   <si>
     <t>DYLAN</t>
   </si>
   <si>
+    <t>JOSE RAUL</t>
+  </si>
+  <si>
+    <t>FEDERICO ABIMAEL</t>
+  </si>
+  <si>
     <t>MIGUEL ANTONIO</t>
   </si>
   <si>
+    <t>DAMIAN</t>
+  </si>
+  <si>
     <t>ARTHUR RICHARD</t>
   </si>
   <si>
+    <t>ROGGER JUSEFH</t>
+  </si>
+  <si>
     <t>ERIC</t>
   </si>
   <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>KARLA ABIGAIL</t>
+  </si>
+  <si>
     <t>AARON MIGUEL</t>
   </si>
   <si>
+    <t>GUILLERMO JESUS</t>
+  </si>
+  <si>
+    <t>JORGE IVAN</t>
+  </si>
+  <si>
+    <t>JARED ABRAHAM</t>
+  </si>
+  <si>
+    <t>JULIAN DAVID</t>
+  </si>
+  <si>
+    <t>JOSE EMMANUEL</t>
+  </si>
+  <si>
+    <t>OLAY</t>
+  </si>
+  <si>
+    <t>ABIEL NEFTALI</t>
+  </si>
+  <si>
+    <t>CARLOS</t>
+  </si>
+  <si>
     <t>DANIEL</t>
-  </si>
-  <si>
-    <t>ALVARADO</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CRESCENCIO</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>PALESTINO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>TOLEDO</t>
-  </si>
-  <si>
-    <t>XOCHICALE</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>LOMAS</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>TEQUILIQUIHUA</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>AXEL MICHAELL</t>
-  </si>
-  <si>
-    <t>ALVARO OZIEL</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>SIMON</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t>JUAN PABLO</t>
-  </si>
-  <si>
-    <t>JOSE RAUL</t>
-  </si>
-  <si>
-    <t>FEDERICO ABIMAEL</t>
-  </si>
-  <si>
-    <t>DAMIAN</t>
-  </si>
-  <si>
-    <t>ROGGER JUSEFH</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>KARLA ABIGAIL</t>
-  </si>
-  <si>
-    <t>GUILLERMO JESUS</t>
-  </si>
-  <si>
-    <t>JORGE IVAN</t>
-  </si>
-  <si>
-    <t>JARED ABRAHAM</t>
-  </si>
-  <si>
-    <t>JULIAN DAVID</t>
-  </si>
-  <si>
-    <t>JOSE EMMANUEL</t>
-  </si>
-  <si>
-    <t>OLAY</t>
-  </si>
-  <si>
-    <t>ABIEL NEFTALI</t>
-  </si>
-  <si>
-    <t>CARLOS</t>
   </si>
   <si>
     <t>JOSE ANTONIO</t>
@@ -1385,7 +1385,7 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C10">
         <v>10</v>
@@ -1403,7 +1403,7 @@
         <v>6</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I10">
         <v>7</v>
@@ -1439,7 +1439,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U10">
         <v>9</v>
@@ -1462,7 +1462,7 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C11">
         <v>7</v>
@@ -1480,7 +1480,7 @@
         <v>6</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -1516,7 +1516,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U11">
         <v>7</v>
@@ -1770,7 +1770,7 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C15">
         <v>8</v>
@@ -1788,7 +1788,7 @@
         <v>6</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I15">
         <v>9</v>
@@ -1824,7 +1824,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U15">
         <v>9</v>
@@ -1847,7 +1847,7 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C16">
         <v>5</v>
@@ -1865,7 +1865,7 @@
         <v>5</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I16">
         <v>5</v>
@@ -1901,7 +1901,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U16">
         <v>5</v>
@@ -2001,7 +2001,7 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C18">
         <v>5</v>
@@ -2019,7 +2019,7 @@
         <v>5</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I18">
         <v>5</v>
@@ -2055,7 +2055,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U18">
         <v>5</v>
@@ -2309,7 +2309,7 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C22">
         <v>5</v>
@@ -2327,7 +2327,7 @@
         <v>5</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I22">
         <v>5</v>
@@ -2363,7 +2363,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U22">
         <v>5</v>
@@ -2925,7 +2925,7 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C30">
         <v>5</v>
@@ -2943,7 +2943,7 @@
         <v>7</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I30">
         <v>6</v>
@@ -2979,7 +2979,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U30">
         <v>5</v>
@@ -3322,25 +3322,25 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>63.33</v>
+        <v>66.67</v>
       </c>
       <c r="G3">
-        <v>13.33</v>
+        <v>33.33</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="I3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>23.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3478,7 +3478,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3503,146 +3503,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>22330051920034</v>
-      </c>
-      <c r="B2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330051920035</v>
-      </c>
-      <c r="B3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>22330051920038</v>
-      </c>
-      <c r="B4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22330051920189</v>
-      </c>
-      <c r="B5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920325</v>
-      </c>
-      <c r="B6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D6" t="s">
-        <v>79</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920043</v>
-      </c>
-      <c r="B7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>22330051920049</v>
-      </c>
-      <c r="B8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8" t="s">
-        <v>81</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -3678,132 +3538,132 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>22330051920034</v>
+        <v>22330051920029</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>22330051920035</v>
+        <v>22330051920030</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>22330051920038</v>
+        <v>22330051920031</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>22330051920189</v>
+        <v>22330051920032</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>22330051920325</v>
+        <v>22330051920033</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>22330051920043</v>
+        <v>22330051920323</v>
       </c>
       <c r="B7" t="s">
         <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>22330051920049</v>
+        <v>22330051920034</v>
       </c>
       <c r="B8" t="s">
         <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>22330051920029</v>
+        <v>22330051920035</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D9" t="s">
         <v>117</v>
@@ -3814,13 +3674,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>22330051920030</v>
+        <v>22330051920036</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s">
         <v>118</v>
@@ -3831,13 +3691,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>22330051920031</v>
+        <v>22330051920037</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
         <v>119</v>
@@ -3848,10 +3708,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>22330051920032</v>
+        <v>22330051920038</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
         <v>94</v>
@@ -3865,13 +3725,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>22330051920033</v>
+        <v>22330051920331</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D13" t="s">
         <v>121</v>
@@ -3882,13 +3742,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>22330051920323</v>
+        <v>22330051920189</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
         <v>122</v>
@@ -3899,13 +3759,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>22330051920036</v>
+        <v>22330051920039</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D15" t="s">
         <v>123</v>
@@ -3916,13 +3776,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>22330051920037</v>
+        <v>22330051920325</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="D16" t="s">
         <v>124</v>
@@ -3933,13 +3793,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>22330051920331</v>
+        <v>22330051920040</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
         <v>125</v>
@@ -3950,13 +3810,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>22330051920039</v>
+        <v>22330051920041</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
         <v>126</v>
@@ -3967,13 +3827,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>22330051920040</v>
+        <v>22330051920043</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="D19" t="s">
         <v>127</v>
@@ -3984,13 +3844,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>22330051920041</v>
+        <v>22330051920042</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D20" t="s">
         <v>128</v>
@@ -4001,13 +3861,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>22330051920042</v>
+        <v>22330051920327</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D21" t="s">
         <v>129</v>
@@ -4018,13 +3878,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>22330051920327</v>
+        <v>22330051920044</v>
       </c>
       <c r="B22" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="D22" t="s">
         <v>130</v>
@@ -4035,13 +3895,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>22330051920044</v>
+        <v>22330051920045</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="C23" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D23" t="s">
         <v>131</v>
@@ -4052,13 +3912,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>22330051920045</v>
+        <v>22330051920046</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D24" t="s">
         <v>132</v>
@@ -4069,13 +3929,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>22330051920046</v>
+        <v>22330051920328</v>
       </c>
       <c r="B25" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="D25" t="s">
         <v>133</v>
@@ -4086,13 +3946,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>22330051920328</v>
+        <v>22330051920047</v>
       </c>
       <c r="B26" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="D26" t="s">
         <v>134</v>
@@ -4103,13 +3963,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>22330051920047</v>
+        <v>22330051920048</v>
       </c>
       <c r="B27" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D27" t="s">
         <v>135</v>
@@ -4120,13 +3980,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>22330051920048</v>
+        <v>22330051920049</v>
       </c>
       <c r="B28" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D28" t="s">
         <v>136</v>
@@ -4140,10 +4000,10 @@
         <v>22330051920329</v>
       </c>
       <c r="B29" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="C29" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D29" t="s">
         <v>137</v>
@@ -4157,10 +4017,10 @@
         <v>22330051920050</v>
       </c>
       <c r="B30" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D30" t="s">
         <v>138</v>
@@ -4174,10 +4034,10 @@
         <v>22330051920051</v>
       </c>
       <c r="B31" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="C31" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D31" t="s">
         <v>139</v>
@@ -4193,7 +4053,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4225,16 +4085,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920034</v>
+        <v>22330051920035</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -4243,21 +4103,21 @@
         <v>52</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920034</v>
+        <v>22330051920035</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -4271,16 +4131,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920035</v>
+        <v>22330051920327</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>129</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -4289,21 +4149,21 @@
         <v>52</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920035</v>
+        <v>22330051920327</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>129</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -4317,22 +4177,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920327</v>
+        <v>22330051920034</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4340,22 +4200,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920327</v>
+        <v>22330051920038</v>
       </c>
       <c r="B7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" t="s">
         <v>94</v>
       </c>
-      <c r="C7" t="s">
-        <v>108</v>
-      </c>
       <c r="D7" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4363,36 +4223,36 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920038</v>
+        <v>22330051920039</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>77</v>
+        <v>123</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920039</v>
+        <v>22330051920041</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D9" t="s">
         <v>126</v>
@@ -4409,16 +4269,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920041</v>
+        <v>22330051920046</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -4427,29 +4287,6 @@
         <v>51</v>
       </c>
       <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920046</v>
-      </c>
-      <c r="B11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" t="s">
-        <v>111</v>
-      </c>
-      <c r="D11" t="s">
-        <v>133</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G11">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1BM - Estadisticos 20221.xlsx
+++ b/grupos/1BM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="140">
   <si>
     <t>Materia</t>
   </si>
@@ -179,16 +179,16 @@
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
+    <t>Herrera Serrano Mayra Iliana</t>
+  </si>
+  <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
     <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>Herrera Serrano Mayra Iliana</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
     <t>NC</t>
@@ -974,7 +974,7 @@
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -1051,7 +1051,7 @@
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>9</v>
@@ -1128,7 +1128,7 @@
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
         <v>7</v>
@@ -1205,7 +1205,7 @@
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>9</v>
@@ -1282,7 +1282,7 @@
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -1359,7 +1359,7 @@
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -1436,7 +1436,7 @@
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T10">
         <v>6</v>
@@ -1454,7 +1454,7 @@
         <v>6</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1513,7 +1513,7 @@
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T11">
         <v>5</v>
@@ -1590,7 +1590,7 @@
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>9</v>
@@ -1667,7 +1667,7 @@
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
         <v>9</v>
@@ -1744,7 +1744,7 @@
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T14">
         <v>7</v>
@@ -1821,7 +1821,7 @@
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T15">
         <v>5</v>
@@ -1898,7 +1898,7 @@
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
         <v>5</v>
@@ -1916,7 +1916,7 @@
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1975,7 +1975,7 @@
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
         <v>7</v>
@@ -2052,7 +2052,7 @@
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T18">
         <v>5</v>
@@ -2129,7 +2129,7 @@
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
         <v>7</v>
@@ -2206,7 +2206,7 @@
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <v>7</v>
@@ -2283,7 +2283,7 @@
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
         <v>9</v>
@@ -2360,7 +2360,7 @@
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T22">
         <v>5</v>
@@ -2437,7 +2437,7 @@
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T23">
         <v>5</v>
@@ -2514,7 +2514,7 @@
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T24">
         <v>5</v>
@@ -2532,7 +2532,7 @@
         <v>7</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2591,7 +2591,7 @@
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T25">
         <v>5</v>
@@ -2668,7 +2668,7 @@
         <v>-1</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T26">
         <v>8</v>
@@ -2745,7 +2745,7 @@
         <v>-1</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
         <v>5</v>
@@ -2763,7 +2763,7 @@
         <v>5</v>
       </c>
       <c r="Y27">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2822,7 +2822,7 @@
         <v>-1</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
         <v>7</v>
@@ -2840,7 +2840,7 @@
         <v>6</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2899,7 +2899,7 @@
         <v>-1</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T29">
         <v>9</v>
@@ -2976,7 +2976,7 @@
         <v>-1</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T30">
         <v>5</v>
@@ -3053,7 +3053,7 @@
         <v>-1</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T31">
         <v>8</v>
@@ -3130,7 +3130,7 @@
         <v>-1</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T32">
         <v>8</v>
@@ -3207,7 +3207,7 @@
         <v>-1</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T33">
         <v>9</v>
@@ -3345,7 +3345,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>53</v>
@@ -3366,7 +3366,7 @@
         <v>16.67</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3377,7 +3377,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
@@ -3386,19 +3386,19 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>83.33</v>
+        <v>86.67</v>
       </c>
       <c r="G5">
-        <v>16.67</v>
+        <v>13.33</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3409,7 +3409,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
@@ -3430,7 +3430,7 @@
         <v>13.33</v>
       </c>
       <c r="H6">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3441,7 +3441,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>56</v>
@@ -3450,19 +3450,19 @@
         <v>30</v>
       </c>
       <c r="D7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>86.67</v>
+        <v>90</v>
       </c>
       <c r="G7">
-        <v>13.33</v>
+        <v>10</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4053,7 +4053,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4177,22 +4177,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920034</v>
+        <v>22330051920047</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="D6" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4200,22 +4200,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920038</v>
+        <v>22330051920047</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="D7" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4223,16 +4223,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920039</v>
+        <v>22330051920034</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -4246,22 +4246,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920041</v>
+        <v>22330051920038</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4269,16 +4269,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920046</v>
+        <v>22330051920039</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -4287,6 +4287,52 @@
         <v>51</v>
       </c>
       <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920041</v>
+      </c>
+      <c r="B11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" t="s">
+        <v>126</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920046</v>
+      </c>
+      <c r="B12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" t="s">
+        <v>132</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1BM - Estadisticos 20221.xlsx
+++ b/grupos/1BM - Estadisticos 20221.xlsx
@@ -971,7 +971,7 @@
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
         <v>8</v>
@@ -1048,7 +1048,7 @@
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
         <v>10</v>
@@ -1125,7 +1125,7 @@
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
         <v>8</v>
@@ -1202,7 +1202,7 @@
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
         <v>10</v>
@@ -1279,7 +1279,7 @@
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
         <v>10</v>
@@ -1356,7 +1356,7 @@
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S9">
         <v>6</v>
@@ -1587,7 +1587,7 @@
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S12">
         <v>8</v>
@@ -1664,7 +1664,7 @@
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
         <v>8</v>
@@ -1741,7 +1741,7 @@
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
         <v>6</v>
@@ -2126,7 +2126,7 @@
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
         <v>8</v>
@@ -2280,7 +2280,7 @@
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
         <v>8</v>
@@ -2819,7 +2819,7 @@
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S28">
         <v>8</v>
@@ -2896,7 +2896,7 @@
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S29">
         <v>7</v>
@@ -2914,7 +2914,7 @@
         <v>9</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y29">
         <v>7</v>
@@ -3050,7 +3050,7 @@
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S31">
         <v>8</v>
@@ -3204,7 +3204,7 @@
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S33">
         <v>8</v>

--- a/grupos/1BM - Estadisticos 20221.xlsx
+++ b/grupos/1BM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="140">
   <si>
     <t>Materia</t>
   </si>
@@ -173,22 +173,22 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
-    <t>Jiménez Nieto Enrique</t>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
   </si>
   <si>
     <t>Herrera Serrano Mayra Iliana</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
-    <t>Velasco Sánchez David</t>
   </si>
   <si>
     <t>NC</t>
@@ -962,10 +962,10 @@
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
         <v>-1</v>
@@ -980,7 +980,7 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V4">
         <v>9</v>
@@ -1039,10 +1039,10 @@
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
         <v>-1</v>
@@ -1057,7 +1057,7 @@
         <v>9</v>
       </c>
       <c r="U5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V5">
         <v>9</v>
@@ -1116,10 +1116,10 @@
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
         <v>-1</v>
@@ -1134,7 +1134,7 @@
         <v>7</v>
       </c>
       <c r="U6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>8</v>
@@ -1193,10 +1193,10 @@
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
         <v>-1</v>
@@ -1270,10 +1270,10 @@
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
         <v>-1</v>
@@ -1291,7 +1291,7 @@
         <v>10</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1347,10 +1347,10 @@
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
         <v>-1</v>
@@ -1368,7 +1368,7 @@
         <v>9</v>
       </c>
       <c r="V9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>8</v>
@@ -1424,16 +1424,16 @@
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S10">
         <v>6</v>
@@ -1442,10 +1442,10 @@
         <v>6</v>
       </c>
       <c r="U10">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W10">
         <v>8</v>
@@ -1504,13 +1504,13 @@
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S11">
         <v>7</v>
@@ -1522,13 +1522,13 @@
         <v>7</v>
       </c>
       <c r="V11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W11">
         <v>7</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y11">
         <v>6</v>
@@ -1578,10 +1578,10 @@
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
         <v>-1</v>
@@ -1596,7 +1596,7 @@
         <v>9</v>
       </c>
       <c r="U12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V12">
         <v>8</v>
@@ -1655,10 +1655,10 @@
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
         <v>-1</v>
@@ -1673,7 +1673,7 @@
         <v>9</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V13">
         <v>8</v>
@@ -1732,10 +1732,10 @@
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
         <v>-1</v>
@@ -1750,7 +1750,7 @@
         <v>7</v>
       </c>
       <c r="U14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>8</v>
@@ -1809,16 +1809,16 @@
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S15">
         <v>6</v>
@@ -1827,10 +1827,10 @@
         <v>5</v>
       </c>
       <c r="U15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>7</v>
@@ -1886,16 +1886,16 @@
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S16">
         <v>7</v>
@@ -1913,7 +1913,7 @@
         <v>5</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y16">
         <v>6</v>
@@ -1963,16 +1963,16 @@
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S17">
         <v>9</v>
@@ -1984,7 +1984,7 @@
         <v>6</v>
       </c>
       <c r="V17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>6</v>
@@ -2040,16 +2040,16 @@
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S18">
         <v>7</v>
@@ -2117,10 +2117,10 @@
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
         <v>-1</v>
@@ -2135,7 +2135,7 @@
         <v>7</v>
       </c>
       <c r="U19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>7</v>
@@ -2197,13 +2197,13 @@
         <v>-1</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S20">
         <v>8</v>
@@ -2215,13 +2215,13 @@
         <v>8</v>
       </c>
       <c r="V20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W20">
         <v>7</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>7</v>
@@ -2271,10 +2271,10 @@
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q21">
         <v>-1</v>
@@ -2289,10 +2289,10 @@
         <v>9</v>
       </c>
       <c r="U21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>7</v>
@@ -2348,16 +2348,16 @@
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
         <v>6</v>
@@ -2369,13 +2369,13 @@
         <v>5</v>
       </c>
       <c r="V22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W22">
         <v>5</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2425,16 +2425,16 @@
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q23">
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S23">
         <v>7</v>
@@ -2443,7 +2443,7 @@
         <v>5</v>
       </c>
       <c r="U23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>5</v>
@@ -2502,16 +2502,16 @@
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S24">
         <v>7</v>
@@ -2529,7 +2529,7 @@
         <v>8</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y24">
         <v>7</v>
@@ -2579,16 +2579,16 @@
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q25">
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S25">
         <v>6</v>
@@ -2597,7 +2597,7 @@
         <v>5</v>
       </c>
       <c r="U25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V25">
         <v>5</v>
@@ -2606,7 +2606,7 @@
         <v>7</v>
       </c>
       <c r="X25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y25">
         <v>6</v>
@@ -2656,16 +2656,16 @@
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S26">
         <v>6</v>
@@ -2674,16 +2674,16 @@
         <v>8</v>
       </c>
       <c r="U26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W26">
         <v>8</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y26">
         <v>6</v>
@@ -2733,16 +2733,16 @@
         <v>-1</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S27">
         <v>8</v>
@@ -2754,13 +2754,13 @@
         <v>7</v>
       </c>
       <c r="V27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W27">
         <v>7</v>
       </c>
       <c r="X27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y27">
         <v>6</v>
@@ -2810,10 +2810,10 @@
         <v>-1</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q28">
         <v>-1</v>
@@ -2828,7 +2828,7 @@
         <v>7</v>
       </c>
       <c r="U28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V28">
         <v>8</v>
@@ -2887,10 +2887,10 @@
         <v>-1</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q29">
         <v>-1</v>
@@ -2905,10 +2905,10 @@
         <v>9</v>
       </c>
       <c r="U29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W29">
         <v>9</v>
@@ -2964,16 +2964,16 @@
         <v>-1</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q30">
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S30">
         <v>7</v>
@@ -2991,7 +2991,7 @@
         <v>5</v>
       </c>
       <c r="X30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y30">
         <v>6</v>
@@ -3041,10 +3041,10 @@
         <v>-1</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q31">
         <v>-1</v>
@@ -3062,7 +3062,7 @@
         <v>9</v>
       </c>
       <c r="V31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W31">
         <v>8</v>
@@ -3118,16 +3118,16 @@
         <v>-1</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q32">
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S32">
         <v>7</v>
@@ -3136,16 +3136,16 @@
         <v>8</v>
       </c>
       <c r="U32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W32">
         <v>9</v>
       </c>
       <c r="X32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y32">
         <v>6</v>
@@ -3195,10 +3195,10 @@
         <v>-1</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q33">
         <v>-1</v>
@@ -3281,7 +3281,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>51</v>
@@ -3290,19 +3290,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>60</v>
+        <v>66.67</v>
       </c>
       <c r="G2">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3313,7 +3313,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>52</v>
@@ -3322,19 +3322,19 @@
         <v>30</v>
       </c>
       <c r="D3">
+        <v>24</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>80</v>
+      </c>
+      <c r="G3">
         <v>20</v>
       </c>
-      <c r="E3">
-        <v>10</v>
-      </c>
-      <c r="F3">
-        <v>66.67</v>
-      </c>
-      <c r="G3">
-        <v>33.33</v>
-      </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3345,7 +3345,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>53</v>
@@ -3354,19 +3354,19 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>83.33</v>
+        <v>80</v>
       </c>
       <c r="G4">
-        <v>16.67</v>
+        <v>20</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3409,7 +3409,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
@@ -3418,19 +3418,19 @@
         <v>30</v>
       </c>
       <c r="D6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>86.67</v>
+        <v>90</v>
       </c>
       <c r="G6">
-        <v>13.33</v>
+        <v>10</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3441,7 +3441,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>56</v>
@@ -3450,19 +3450,19 @@
         <v>30</v>
       </c>
       <c r="D7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>90</v>
+        <v>93.33</v>
       </c>
       <c r="G7">
-        <v>10</v>
+        <v>6.67</v>
       </c>
       <c r="H7">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4053,7 +4053,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920035</v>
+        <v>22330051920327</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4108,22 +4108,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920035</v>
+        <v>22330051920327</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4131,22 +4131,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920327</v>
+        <v>22330051920035</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4154,22 +4154,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920327</v>
+        <v>22330051920036</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4177,22 +4177,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920047</v>
+        <v>22330051920038</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4212,127 +4212,12 @@
         <v>134</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920034</v>
-      </c>
-      <c r="B8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920038</v>
-      </c>
-      <c r="B9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" t="s">
-        <v>94</v>
-      </c>
-      <c r="D9" t="s">
-        <v>120</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>52</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920039</v>
-      </c>
-      <c r="B10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" t="s">
-        <v>96</v>
-      </c>
-      <c r="D10" t="s">
-        <v>123</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>51</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920041</v>
-      </c>
-      <c r="B11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11" t="s">
-        <v>98</v>
-      </c>
-      <c r="D11" t="s">
-        <v>126</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920046</v>
-      </c>
-      <c r="B12" t="s">
-        <v>82</v>
-      </c>
-      <c r="C12" t="s">
-        <v>103</v>
-      </c>
-      <c r="D12" t="s">
-        <v>132</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>51</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1BM - Estadisticos 20221.xlsx
+++ b/grupos/1BM - Estadisticos 20221.xlsx
@@ -968,7 +968,7 @@
         <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
         <v>8</v>
@@ -986,7 +986,7 @@
         <v>9</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>7</v>
@@ -1045,7 +1045,7 @@
         <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>9</v>
@@ -1122,7 +1122,7 @@
         <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R6">
         <v>6</v>
@@ -1199,7 +1199,7 @@
         <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
         <v>10</v>
@@ -1276,7 +1276,7 @@
         <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
         <v>10</v>
@@ -1353,7 +1353,7 @@
         <v>5</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
         <v>6</v>
@@ -1430,7 +1430,7 @@
         <v>7</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R10">
         <v>6</v>
@@ -1448,7 +1448,7 @@
         <v>6</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>6</v>
@@ -1507,7 +1507,7 @@
         <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
         <v>6</v>
@@ -1584,7 +1584,7 @@
         <v>8</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R12">
         <v>6</v>
@@ -1602,7 +1602,7 @@
         <v>8</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>6</v>
@@ -1661,7 +1661,7 @@
         <v>7</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
         <v>9</v>
@@ -1738,7 +1738,7 @@
         <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R14">
         <v>8</v>
@@ -1815,7 +1815,7 @@
         <v>6</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
         <v>6</v>
@@ -1892,7 +1892,7 @@
         <v>7</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R16">
         <v>5</v>
@@ -1969,7 +1969,7 @@
         <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
         <v>7</v>
@@ -2046,7 +2046,7 @@
         <v>5</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R18">
         <v>5</v>
@@ -2123,7 +2123,7 @@
         <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
         <v>8</v>
@@ -2200,7 +2200,7 @@
         <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>6</v>
@@ -2218,7 +2218,7 @@
         <v>6</v>
       </c>
       <c r="W20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X20">
         <v>6</v>
@@ -2277,7 +2277,7 @@
         <v>6</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
         <v>8</v>
@@ -2354,7 +2354,7 @@
         <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
         <v>7</v>
@@ -2431,7 +2431,7 @@
         <v>5</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R23">
         <v>6</v>
@@ -2508,7 +2508,7 @@
         <v>6</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
         <v>6</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R25">
         <v>7</v>
@@ -2603,7 +2603,7 @@
         <v>5</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X25">
         <v>6</v>
@@ -2662,7 +2662,7 @@
         <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
         <v>6</v>
@@ -2739,7 +2739,7 @@
         <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>7</v>
@@ -2757,7 +2757,7 @@
         <v>7</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>6</v>
@@ -2816,7 +2816,7 @@
         <v>7</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R28">
         <v>7</v>
@@ -2834,7 +2834,7 @@
         <v>8</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>6</v>
@@ -2893,7 +2893,7 @@
         <v>5</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R29">
         <v>6</v>
@@ -2911,7 +2911,7 @@
         <v>7</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>7</v>
@@ -2970,7 +2970,7 @@
         <v>6</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R30">
         <v>7</v>
@@ -3047,7 +3047,7 @@
         <v>7</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
         <v>8</v>
@@ -3124,7 +3124,7 @@
         <v>5</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R32">
         <v>6</v>
@@ -3142,7 +3142,7 @@
         <v>7</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X32">
         <v>6</v>
@@ -3201,7 +3201,7 @@
         <v>7</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>8</v>
@@ -3398,7 +3398,7 @@
         <v>13.33</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="I5">
         <v>0</v>

--- a/grupos/1BM - Estadisticos 20221.xlsx
+++ b/grupos/1BM - Estadisticos 20221.xlsx
@@ -173,22 +173,22 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
+    <t>Herrera Serrano Mayra Iliana</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
     <t>NC</t>
@@ -959,7 +959,7 @@
         <v>7</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>9</v>
@@ -1036,7 +1036,7 @@
         <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
         <v>8</v>
@@ -1113,7 +1113,7 @@
         <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O6">
         <v>6</v>
@@ -1190,7 +1190,7 @@
         <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
         <v>10</v>
@@ -1267,7 +1267,7 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
         <v>10</v>
@@ -1344,7 +1344,7 @@
         <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
         <v>10</v>
@@ -1362,7 +1362,7 @@
         <v>6</v>
       </c>
       <c r="T9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U9">
         <v>9</v>
@@ -1421,7 +1421,7 @@
         <v>7</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
         <v>5</v>
@@ -1439,7 +1439,7 @@
         <v>6</v>
       </c>
       <c r="T10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U10">
         <v>7</v>
@@ -1483,7 +1483,7 @@
         <v>5</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
         <v>5</v>
@@ -1498,10 +1498,10 @@
         <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P11">
         <v>8</v>
@@ -1516,7 +1516,7 @@
         <v>7</v>
       </c>
       <c r="T11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U11">
         <v>7</v>
@@ -1575,7 +1575,7 @@
         <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
         <v>5</v>
@@ -1593,7 +1593,7 @@
         <v>8</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U12">
         <v>5</v>
@@ -1652,7 +1652,7 @@
         <v>7</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
         <v>6</v>
@@ -1729,7 +1729,7 @@
         <v>6</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
         <v>7</v>
@@ -1747,7 +1747,7 @@
         <v>6</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U14">
         <v>8</v>
@@ -1806,7 +1806,7 @@
         <v>6</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
         <v>5</v>
@@ -1824,7 +1824,7 @@
         <v>6</v>
       </c>
       <c r="T15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U15">
         <v>7</v>
@@ -1883,7 +1883,7 @@
         <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
         <v>6</v>
@@ -1901,7 +1901,7 @@
         <v>7</v>
       </c>
       <c r="T16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>5</v>
@@ -1960,7 +1960,7 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
         <v>7</v>
@@ -1978,7 +1978,7 @@
         <v>9</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>6</v>
@@ -2037,7 +2037,7 @@
         <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
         <v>5</v>
@@ -2114,7 +2114,7 @@
         <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
         <v>8</v>
@@ -2176,7 +2176,7 @@
         <v>5</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
         <v>6</v>
@@ -2191,10 +2191,10 @@
         <v>7</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
         <v>7</v>
@@ -2212,7 +2212,7 @@
         <v>7</v>
       </c>
       <c r="U20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>6</v>
@@ -2268,7 +2268,7 @@
         <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
         <v>5</v>
@@ -2363,7 +2363,7 @@
         <v>6</v>
       </c>
       <c r="T22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>5</v>
@@ -2422,7 +2422,7 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
         <v>6</v>
@@ -2440,7 +2440,7 @@
         <v>7</v>
       </c>
       <c r="T23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U23">
         <v>6</v>
@@ -2499,7 +2499,7 @@
         <v>7</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
         <v>7</v>
@@ -2517,7 +2517,7 @@
         <v>7</v>
       </c>
       <c r="T24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U24">
         <v>7</v>
@@ -2576,7 +2576,7 @@
         <v>6</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O25">
         <v>5</v>
@@ -2594,7 +2594,7 @@
         <v>6</v>
       </c>
       <c r="T25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U25">
         <v>5</v>
@@ -2653,7 +2653,7 @@
         <v>6</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O26">
         <v>5</v>
@@ -2671,7 +2671,7 @@
         <v>6</v>
       </c>
       <c r="T26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U26">
         <v>7</v>
@@ -2730,7 +2730,7 @@
         <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O27">
         <v>7</v>
@@ -2748,7 +2748,7 @@
         <v>8</v>
       </c>
       <c r="T27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U27">
         <v>7</v>
@@ -2807,7 +2807,7 @@
         <v>6</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
         <v>7</v>
@@ -2825,7 +2825,7 @@
         <v>8</v>
       </c>
       <c r="T28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U28">
         <v>8</v>
@@ -2884,7 +2884,7 @@
         <v>7</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O29">
         <v>5</v>
@@ -2902,7 +2902,7 @@
         <v>7</v>
       </c>
       <c r="T29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U29">
         <v>8</v>
@@ -2961,7 +2961,7 @@
         <v>5</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O30">
         <v>5</v>
@@ -2979,7 +2979,7 @@
         <v>7</v>
       </c>
       <c r="T30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U30">
         <v>5</v>
@@ -3038,7 +3038,7 @@
         <v>7</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O31">
         <v>8</v>
@@ -3115,7 +3115,7 @@
         <v>6</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O32">
         <v>7</v>
@@ -3192,7 +3192,7 @@
         <v>6</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
         <v>10</v>
@@ -3281,7 +3281,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>51</v>
@@ -3290,19 +3290,19 @@
         <v>30</v>
       </c>
       <c r="D2">
+        <v>24</v>
+      </c>
+      <c r="E2">
+        <v>6</v>
+      </c>
+      <c r="F2">
+        <v>80</v>
+      </c>
+      <c r="G2">
         <v>20</v>
       </c>
-      <c r="E2">
-        <v>10</v>
-      </c>
-      <c r="F2">
-        <v>66.67</v>
-      </c>
-      <c r="G2">
-        <v>33.33</v>
-      </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3313,7 +3313,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>52</v>
@@ -3334,7 +3334,7 @@
         <v>20</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3345,7 +3345,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>53</v>
@@ -3354,19 +3354,19 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>80</v>
+        <v>86.67</v>
       </c>
       <c r="G4">
-        <v>20</v>
+        <v>13.33</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3377,7 +3377,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
@@ -3386,19 +3386,19 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>86.67</v>
+        <v>90</v>
       </c>
       <c r="G5">
-        <v>13.33</v>
+        <v>10</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3409,7 +3409,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
@@ -3418,19 +3418,19 @@
         <v>30</v>
       </c>
       <c r="D6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>90</v>
+        <v>93.33</v>
       </c>
       <c r="G6">
-        <v>10</v>
+        <v>6.67</v>
       </c>
       <c r="H6">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3441,7 +3441,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>56</v>
@@ -3450,19 +3450,19 @@
         <v>30</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>93.33</v>
+        <v>96.67</v>
       </c>
       <c r="G7">
-        <v>6.67</v>
+        <v>3.33</v>
       </c>
       <c r="H7">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4085,19 +4085,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920327</v>
+        <v>22330051920044</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
         <v>51</v>
@@ -4108,22 +4108,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920327</v>
+        <v>22330051920044</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4131,22 +4131,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920035</v>
+        <v>22330051920045</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="D4" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4154,22 +4154,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920036</v>
+        <v>22330051920045</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4177,22 +4177,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920038</v>
+        <v>22330051920036</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4200,19 +4200,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920047</v>
+        <v>22330051920327</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
         <v>51</v>
